--- a/Result/profitability/1514.xlsx
+++ b/Result/profitability/1514.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>18.28625</v>
+        <v>18.5025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61625</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>17.3275</v>
+        <v>17.5075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.51</v>
+        <v>0.5475</v>
       </c>
       <c r="N4" t="n">
-        <v>16.4325</v>
+        <v>16.6975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3325</v>
+        <v>0.3575</v>
       </c>
       <c r="N5" t="n">
-        <v>15.4425</v>
+        <v>15.7625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26</v>
+        <v>0.2625</v>
       </c>
       <c r="N6" t="n">
-        <v>15.21125</v>
+        <v>15.595</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>-0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14375</v>
+        <v>0.11875</v>
       </c>
       <c r="N7" t="n">
-        <v>14.6425</v>
+        <v>14.73625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008749999999999994</v>
+        <v>0.03125</v>
       </c>
       <c r="N8" t="n">
-        <v>13.625</v>
+        <v>14.03375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2819</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2233</v>
+      </c>
+      <c r="E75" t="n">
+        <v>587</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>315</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>315</v>
+      </c>
+      <c r="K75" t="n">
+        <v>248</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.79875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.9425</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2465753424657535</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1864310148232611</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2816901408450705</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.559999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1402739726027395</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
